--- a/99_Others/WBS.xlsx
+++ b/99_Others/WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio\99_Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E999166E-FDF4-43AE-9799-C16D0AD53C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042DB170-DFAE-406A-93A8-8F0ECFFDEAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0CEC575C-2CE2-4A91-9FC5-0346F782D22B}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WBS!$B$6:$O$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">WBS!$A$1:$O$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">WBS!$A$1:$O$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">WBS!$6:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -876,6 +876,29 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>架空銀行向けWebアプリ</t>
+    <rPh sb="0" eb="2">
+      <t>カクウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ギンコウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カスタムエラー画面作成</t>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -956,7 +979,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1092,30 +1115,6 @@
       <left style="thin">
         <color theme="0" tint="-0.499984740745262"/>
       </left>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
       <right/>
       <top style="thin">
         <color theme="0" tint="-0.499984740745262"/>
@@ -1138,13 +1137,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1153,58 +1152,43 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -1213,31 +1197,31 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1758,13 +1742,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="double">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color theme="0" tint="-0.499984740745262"/>
@@ -1800,6 +1777,13 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="double">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1851,13 +1835,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B8D8251E-0594-4E6A-B0EC-EDB781E6A459}" name="テーブル2" displayName="テーブル2" ref="B6:O29" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19" headerRowBorderDxfId="17" tableBorderDxfId="18">
-  <autoFilter ref="B6:O29" xr:uid="{B8D8251E-0594-4E6A-B0EC-EDB781E6A459}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B8D8251E-0594-4E6A-B0EC-EDB781E6A459}" name="テーブル2" displayName="テーブル2" ref="B6:O28" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17">
+  <autoFilter ref="B6:O28" xr:uid="{B8D8251E-0594-4E6A-B0EC-EDB781E6A459}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{CC7F0879-1CA0-45C0-9252-4769D93B8B06}" name="#" dataDxfId="16">
       <calculatedColumnFormula>ROW()-6</calculatedColumnFormula>
@@ -2202,7 +2182,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:O36"/>
+  <dimension ref="B2:O35"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="5.5" style="5" customWidth="1"/>
@@ -2220,7 +2200,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="20" t="s">
         <v>24</v>
       </c>
       <c r="L2" s="5" t="s">
@@ -2248,51 +2228,51 @@
       <c r="M5" s="8"/>
     </row>
     <row r="6" spans="2:15" ht="38.25" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="27" t="s">
+      <c r="B6" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="27" t="s">
+      <c r="I6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="27" t="s">
+      <c r="K6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="27" t="s">
+      <c r="L6" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="27" t="s">
+      <c r="M6" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="N6" s="27" t="s">
+      <c r="N6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="O6" s="28" t="s">
+      <c r="O6" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="29">
+      <c r="B7" s="24">
         <f>ROW()-6</f>
         <v>1</v>
       </c>
@@ -2303,10 +2283,10 @@
         <v>6</v>
       </c>
       <c r="E7" s="10"/>
-      <c r="F7" s="33">
+      <c r="F7" s="28">
         <v>4</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="26">
         <v>4</v>
       </c>
       <c r="H7" s="11" t="s">
@@ -2317,17 +2297,17 @@
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="11"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
       <c r="N7" s="12">
-        <f>IFERROR(F7/G7,0)</f>
+        <f t="shared" ref="N7:N28" si="0">IFERROR(F7/G7,0)</f>
         <v>1</v>
       </c>
       <c r="O7" s="13"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B8" s="29">
-        <f t="shared" ref="B8:B29" si="0">ROW()-6</f>
+      <c r="B8" s="24">
+        <f t="shared" ref="B8:B28" si="1">ROW()-6</f>
         <v>2</v>
       </c>
       <c r="C8" s="9">
@@ -2339,10 +2319,10 @@
       <c r="E8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="33">
-        <v>0</v>
-      </c>
-      <c r="G8" s="31">
+      <c r="F8" s="28">
+        <v>0</v>
+      </c>
+      <c r="G8" s="26">
         <v>1</v>
       </c>
       <c r="H8" s="11" t="s">
@@ -2353,12 +2333,12 @@
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="11"/>
-      <c r="L8" s="31">
+      <c r="L8" s="26">
         <v>1</v>
       </c>
-      <c r="M8" s="31"/>
+      <c r="M8" s="26"/>
       <c r="N8" s="12">
-        <f>IFERROR(F8/G8,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O8" s="13" t="s">
@@ -2366,8 +2346,8 @@
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B9" s="29">
-        <f t="shared" si="0"/>
+      <c r="B9" s="24">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="C9" s="9">
@@ -2379,10 +2359,10 @@
       <c r="E9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="33">
-        <v>0</v>
-      </c>
-      <c r="G9" s="31">
+      <c r="F9" s="28">
+        <v>0</v>
+      </c>
+      <c r="G9" s="26">
         <v>1</v>
       </c>
       <c r="H9" s="11" t="s">
@@ -2393,12 +2373,12 @@
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="11"/>
-      <c r="L9" s="31">
+      <c r="L9" s="26">
         <v>2</v>
       </c>
-      <c r="M9" s="31"/>
+      <c r="M9" s="26"/>
       <c r="N9" s="12">
-        <f>IFERROR(F9/G9,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O9" s="13" t="s">
@@ -2406,8 +2386,8 @@
       </c>
     </row>
     <row r="10" spans="2:15" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B10" s="29">
-        <f t="shared" si="0"/>
+      <c r="B10" s="24">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="C10" s="9">
@@ -2419,10 +2399,10 @@
       <c r="E10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="33">
-        <v>0</v>
-      </c>
-      <c r="G10" s="31">
+      <c r="F10" s="28">
+        <v>0</v>
+      </c>
+      <c r="G10" s="26">
         <v>10</v>
       </c>
       <c r="H10" s="11" t="s">
@@ -2433,12 +2413,12 @@
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="11"/>
-      <c r="L10" s="31">
+      <c r="L10" s="26">
         <v>1</v>
       </c>
-      <c r="M10" s="31"/>
+      <c r="M10" s="26"/>
       <c r="N10" s="12">
-        <f>IFERROR(F10/G10,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O10" s="13" t="s">
@@ -2446,8 +2426,8 @@
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B11" s="29">
-        <f t="shared" si="0"/>
+      <c r="B11" s="24">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="C11" s="9">
@@ -2459,10 +2439,10 @@
       <c r="E11" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="33">
-        <v>0</v>
-      </c>
-      <c r="G11" s="31">
+      <c r="F11" s="28">
+        <v>0</v>
+      </c>
+      <c r="G11" s="26">
         <v>10</v>
       </c>
       <c r="H11" s="11" t="s">
@@ -2473,12 +2453,12 @@
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="11"/>
-      <c r="L11" s="31">
+      <c r="L11" s="26">
         <v>1</v>
       </c>
-      <c r="M11" s="31"/>
+      <c r="M11" s="26"/>
       <c r="N11" s="12">
-        <f>IFERROR(F11/G11,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O11" s="13" t="s">
@@ -2486,8 +2466,8 @@
       </c>
     </row>
     <row r="12" spans="2:15" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B12" s="29">
-        <f t="shared" si="0"/>
+      <c r="B12" s="24">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="C12" s="9">
@@ -2499,10 +2479,10 @@
       <c r="E12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="33">
-        <v>0</v>
-      </c>
-      <c r="G12" s="31">
+      <c r="F12" s="28">
+        <v>0</v>
+      </c>
+      <c r="G12" s="26">
         <v>10</v>
       </c>
       <c r="H12" s="11" t="s">
@@ -2513,12 +2493,12 @@
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="11"/>
-      <c r="L12" s="31">
+      <c r="L12" s="26">
         <v>0.25</v>
       </c>
-      <c r="M12" s="31"/>
+      <c r="M12" s="26"/>
       <c r="N12" s="12">
-        <f>IFERROR(F12/G12,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O12" s="13" t="s">
@@ -2526,8 +2506,8 @@
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B13" s="29">
-        <f t="shared" si="0"/>
+      <c r="B13" s="24">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="C13" s="14">
@@ -2537,10 +2517,10 @@
         <v>6</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="32">
+      <c r="F13" s="27">
         <v>4</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="27">
         <v>4</v>
       </c>
       <c r="H13" s="15" t="s">
@@ -2551,19 +2531,19 @@
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
-      <c r="L13" s="32">
+      <c r="L13" s="27">
         <v>0.25</v>
       </c>
-      <c r="M13" s="32"/>
+      <c r="M13" s="27"/>
       <c r="N13" s="12">
-        <f>IFERROR(F13/G13,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O13" s="16"/>
     </row>
     <row r="14" spans="2:15" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B14" s="29">
-        <f t="shared" si="0"/>
+      <c r="B14" s="24">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="C14" s="14">
@@ -2575,10 +2555,10 @@
       <c r="E14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="32">
-        <v>0</v>
-      </c>
-      <c r="G14" s="32">
+      <c r="F14" s="27">
+        <v>0</v>
+      </c>
+      <c r="G14" s="27">
         <v>1</v>
       </c>
       <c r="H14" s="15" t="s">
@@ -2589,19 +2569,19 @@
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="32">
+      <c r="L14" s="27">
         <v>4</v>
       </c>
-      <c r="M14" s="32"/>
+      <c r="M14" s="27"/>
       <c r="N14" s="12">
-        <f>IFERROR(F14/G14,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O14" s="16"/>
     </row>
     <row r="15" spans="2:15" ht="75" x14ac:dyDescent="0.4">
-      <c r="B15" s="29">
-        <f t="shared" si="0"/>
+      <c r="B15" s="24">
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="C15" s="14">
@@ -2613,10 +2593,10 @@
       <c r="E15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="32">
-        <v>0</v>
-      </c>
-      <c r="G15" s="32">
+      <c r="F15" s="27">
+        <v>0</v>
+      </c>
+      <c r="G15" s="27">
         <v>6</v>
       </c>
       <c r="H15" s="15" t="s">
@@ -2627,19 +2607,19 @@
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
-      <c r="L15" s="32">
+      <c r="L15" s="27">
         <v>8</v>
       </c>
-      <c r="M15" s="32"/>
+      <c r="M15" s="27"/>
       <c r="N15" s="12">
-        <f>IFERROR(F15/G15,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O15" s="16"/>
     </row>
     <row r="16" spans="2:15" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B16" s="29">
-        <f t="shared" si="0"/>
+      <c r="B16" s="24">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="C16" s="14">
@@ -2651,10 +2631,10 @@
       <c r="E16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="32">
-        <v>0</v>
-      </c>
-      <c r="G16" s="32">
+      <c r="F16" s="27">
+        <v>0</v>
+      </c>
+      <c r="G16" s="27">
         <v>10</v>
       </c>
       <c r="H16" s="15" t="s">
@@ -2665,19 +2645,19 @@
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
-      <c r="L16" s="32">
+      <c r="L16" s="27">
         <v>2</v>
       </c>
-      <c r="M16" s="32"/>
+      <c r="M16" s="27"/>
       <c r="N16" s="12">
-        <f>IFERROR(F16/G16,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O16" s="16"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B17" s="29">
-        <f t="shared" si="0"/>
+      <c r="B17" s="24">
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="C17" s="14">
@@ -2689,10 +2669,10 @@
       <c r="E17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="32">
-        <v>0</v>
-      </c>
-      <c r="G17" s="32">
+      <c r="F17" s="27">
+        <v>0</v>
+      </c>
+      <c r="G17" s="27">
         <v>10</v>
       </c>
       <c r="H17" s="15" t="s">
@@ -2703,19 +2683,19 @@
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
-      <c r="L17" s="32">
+      <c r="L17" s="27">
         <v>2</v>
       </c>
-      <c r="M17" s="32"/>
+      <c r="M17" s="27"/>
       <c r="N17" s="12">
-        <f>IFERROR(F17/G17,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O17" s="16"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B18" s="29">
-        <f t="shared" si="0"/>
+      <c r="B18" s="24">
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="C18" s="14">
@@ -2727,10 +2707,10 @@
       <c r="E18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="32">
-        <v>0</v>
-      </c>
-      <c r="G18" s="32">
+      <c r="F18" s="27">
+        <v>0</v>
+      </c>
+      <c r="G18" s="27">
         <v>1</v>
       </c>
       <c r="H18" s="15" t="s">
@@ -2741,17 +2721,17 @@
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
       <c r="N18" s="12">
-        <f>IFERROR(F18/G18,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O18" s="16"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B19" s="29">
-        <f t="shared" si="0"/>
+      <c r="B19" s="24">
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="C19" s="14">
@@ -2763,10 +2743,10 @@
       <c r="E19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="32">
-        <v>0</v>
-      </c>
-      <c r="G19" s="32">
+      <c r="F19" s="27">
+        <v>0</v>
+      </c>
+      <c r="G19" s="27">
         <v>4</v>
       </c>
       <c r="H19" s="15" t="s">
@@ -2777,16 +2757,16 @@
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
       <c r="N19" s="12">
-        <f>IFERROR(F19/G19,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O19" s="16"/>
     </row>
     <row r="20" spans="2:15" ht="75" x14ac:dyDescent="0.4">
-      <c r="B20" s="29">
+      <c r="B20" s="24">
         <f>ROW()-6</f>
         <v>14</v>
       </c>
@@ -2799,10 +2779,10 @@
       <c r="E20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="32">
-        <v>0</v>
-      </c>
-      <c r="G20" s="32">
+      <c r="F20" s="27">
+        <v>0</v>
+      </c>
+      <c r="G20" s="27">
         <v>1</v>
       </c>
       <c r="H20" s="15" t="s">
@@ -2813,18 +2793,18 @@
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="32">
+      <c r="L20" s="27">
         <v>4</v>
       </c>
-      <c r="M20" s="32"/>
+      <c r="M20" s="27"/>
       <c r="N20" s="12">
-        <f>IFERROR(F20/G20,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O20" s="16"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B21" s="29">
+      <c r="B21" s="24">
         <f>ROW()-6</f>
         <v>15</v>
       </c>
@@ -2837,10 +2817,10 @@
       <c r="E21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="32">
-        <v>0</v>
-      </c>
-      <c r="G21" s="32">
+      <c r="F21" s="27">
+        <v>0</v>
+      </c>
+      <c r="G21" s="27">
         <v>4</v>
       </c>
       <c r="H21" s="15" t="s">
@@ -2851,18 +2831,18 @@
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="32">
+      <c r="L21" s="27">
         <v>8</v>
       </c>
-      <c r="M21" s="32"/>
+      <c r="M21" s="27"/>
       <c r="N21" s="12">
-        <f>IFERROR(F21/G21,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O21" s="16"/>
     </row>
     <row r="22" spans="2:15" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B22" s="29">
+      <c r="B22" s="24">
         <f>ROW()-6</f>
         <v>16</v>
       </c>
@@ -2875,10 +2855,10 @@
       <c r="E22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F22" s="32">
-        <v>0</v>
-      </c>
-      <c r="G22" s="32">
+      <c r="F22" s="27">
+        <v>0</v>
+      </c>
+      <c r="G22" s="27">
         <v>10</v>
       </c>
       <c r="H22" s="15" t="s">
@@ -2889,18 +2869,18 @@
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="32">
+      <c r="L22" s="27">
         <v>1</v>
       </c>
-      <c r="M22" s="32"/>
+      <c r="M22" s="27"/>
       <c r="N22" s="12">
-        <f>IFERROR(F22/G22,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O22" s="16"/>
     </row>
     <row r="23" spans="2:15" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B23" s="29">
+      <c r="B23" s="24">
         <f>ROW()-6</f>
         <v>17</v>
       </c>
@@ -2913,10 +2893,10 @@
       <c r="E23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="32">
-        <v>0</v>
-      </c>
-      <c r="G23" s="32">
+      <c r="F23" s="27">
+        <v>0</v>
+      </c>
+      <c r="G23" s="27">
         <v>10</v>
       </c>
       <c r="H23" s="15" t="s">
@@ -2927,18 +2907,18 @@
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="32">
+      <c r="L23" s="27">
         <v>1</v>
       </c>
-      <c r="M23" s="32"/>
+      <c r="M23" s="27"/>
       <c r="N23" s="12">
-        <f>IFERROR(F23/G23,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O23" s="16"/>
     </row>
     <row r="24" spans="2:15" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B24" s="29">
+      <c r="B24" s="24">
         <f>ROW()-6</f>
         <v>18</v>
       </c>
@@ -2951,10 +2931,10 @@
       <c r="E24" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="32">
-        <v>0</v>
-      </c>
-      <c r="G24" s="32">
+      <c r="F24" s="27">
+        <v>0</v>
+      </c>
+      <c r="G24" s="27">
         <v>1</v>
       </c>
       <c r="H24" s="15" t="s">
@@ -2965,19 +2945,19 @@
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="32">
+      <c r="L24" s="27">
         <v>1</v>
       </c>
-      <c r="M24" s="32"/>
+      <c r="M24" s="27"/>
       <c r="N24" s="12">
-        <f>IFERROR(F24/G24,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O24" s="16"/>
     </row>
     <row r="25" spans="2:15" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B25" s="29">
-        <f t="shared" si="0"/>
+      <c r="B25" s="24">
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="C25" s="14" t="s">
@@ -2989,10 +2969,10 @@
       <c r="E25" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F25" s="32">
-        <v>0</v>
-      </c>
-      <c r="G25" s="32">
+      <c r="F25" s="27">
+        <v>0</v>
+      </c>
+      <c r="G25" s="27">
         <v>1</v>
       </c>
       <c r="H25" s="15" t="s">
@@ -3003,19 +2983,19 @@
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
-      <c r="L25" s="32">
+      <c r="L25" s="27">
         <v>2</v>
       </c>
-      <c r="M25" s="32"/>
+      <c r="M25" s="27"/>
       <c r="N25" s="12">
-        <f>IFERROR(F25/G25,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O25" s="16"/>
     </row>
     <row r="26" spans="2:15" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B26" s="29">
-        <f t="shared" si="0"/>
+      <c r="B26" s="24">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="C26" s="14" t="s">
@@ -3027,10 +3007,10 @@
       <c r="E26" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="32">
-        <v>0</v>
-      </c>
-      <c r="G26" s="32">
+      <c r="F26" s="27">
+        <v>0</v>
+      </c>
+      <c r="G26" s="27">
         <v>1</v>
       </c>
       <c r="H26" s="15" t="s">
@@ -3041,19 +3021,19 @@
       </c>
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="32">
+      <c r="L26" s="27">
         <v>2</v>
       </c>
-      <c r="M26" s="32"/>
+      <c r="M26" s="27"/>
       <c r="N26" s="12">
-        <f>IFERROR(F26/G26,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O26" s="16"/>
     </row>
     <row r="27" spans="2:15" ht="93.75" x14ac:dyDescent="0.4">
-      <c r="B27" s="29">
-        <f t="shared" si="0"/>
+      <c r="B27" s="24">
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="C27" s="14" t="s">
@@ -3065,10 +3045,10 @@
       <c r="E27" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="32">
-        <v>0</v>
-      </c>
-      <c r="G27" s="32">
+      <c r="F27" s="27">
+        <v>0</v>
+      </c>
+      <c r="G27" s="27">
         <v>1</v>
       </c>
       <c r="H27" s="15" t="s">
@@ -3079,26 +3059,32 @@
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="15"/>
-      <c r="L27" s="32">
+      <c r="L27" s="27">
         <v>4</v>
       </c>
-      <c r="M27" s="32"/>
+      <c r="M27" s="27"/>
       <c r="N27" s="12">
-        <f>IFERROR(F27/G27,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O27" s="16"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B28" s="29">
-        <f t="shared" si="0"/>
+      <c r="B28" s="24">
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
+      <c r="C28" s="14">
+        <v>5</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
@@ -3106,95 +3092,73 @@
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
       <c r="N28" s="12">
-        <f>IFERROR(F28/G28,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O28" s="16"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B29" s="29">
-        <f t="shared" si="0"/>
-        <v>23</v>
+      <c r="B29" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="C29" s="17"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="20">
-        <f>IFERROR(F29/G29,0)</f>
-        <v>0</v>
-      </c>
-      <c r="O29" s="21"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="17"/>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B30" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="23"/>
-      <c r="O30" s="22"/>
+      <c r="B30" s="5" t="str">
+        <f ca="1">_xlfn.CONCAT("PDF出力・印刷日："&amp;TEXT(TODAY(),"YYYY/MM/DD"))</f>
+        <v>PDF出力・印刷日：2026/01/12</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="17"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B31" s="5" t="str">
-        <f ca="1">_xlfn.CONCAT("PDF出力・印刷日："&amp;TEXT(TODAY(),"YYYY/MM/DD"))</f>
-        <v>PDF出力・印刷日：2026/01/02</v>
-      </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="23"/>
-      <c r="O31" s="22"/>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="23"/>
-      <c r="O32" s="22"/>
-    </row>
-    <row r="34" spans="12:15" x14ac:dyDescent="0.4">
-      <c r="O34" s="24"/>
-    </row>
-    <row r="36" spans="12:15" x14ac:dyDescent="0.4">
-      <c r="L36" s="30"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="17"/>
+    </row>
+    <row r="33" spans="12:15" x14ac:dyDescent="0.4">
+      <c r="O33" s="19"/>
+    </row>
+    <row r="35" spans="12:15" x14ac:dyDescent="0.4">
+      <c r="L35" s="25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B7:O24 B27:O163 B25:G26 I25:O26">
+  <conditionalFormatting sqref="B7:O24 B25:G26 I25:O26 B27:O27 B29:O162 E28:O28 B28:C28">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>$N7=1</formula>
     </cfRule>
@@ -3215,7 +3179,7 @@
     <oddFooter>&amp;P / &amp;N ページ</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="32" max="14" man="1"/>
+    <brk id="31" max="14" man="1"/>
   </rowBreaks>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
